--- a/sequences/retrieval_blockB_fixed-middle-10_01.xlsx
+++ b/sequences/retrieval_blockB_fixed-middle-10_01.xlsx
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -557,65 +557,43 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -640,41 +618,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -682,7 +660,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
         <v>1.5</v>
@@ -692,13 +670,13 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -723,12 +701,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -744,16 +722,16 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -764,13 +742,13 @@
         <v>0.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -778,7 +756,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,23 +776,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_18.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -828,32 +810,36 @@
         </is>
       </c>
       <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0.2</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -873,21 +859,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -896,17 +894,19 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -934,70 +934,48 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1017,62 +995,70 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
       <c r="P8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1092,27 +1078,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1126,36 +1108,32 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0.2</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1175,43 +1153,65 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" t="n">
-        <v>10</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1257,16 +1257,16 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1277,13 +1277,13 @@
         <v>0.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1332,16 +1332,16 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         <v>0.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1394,62 +1394,54 @@
           <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0.2</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
         <v>9</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1469,48 +1461,70 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1530,54 +1544,40 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1605,41 +1605,41 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
         <v>1.5</v>
@@ -1657,13 +1657,13 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1708,29 +1708,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>4</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>7</v>
       </c>
       <c r="P17" t="n">
         <v>1.5</v>
@@ -1740,13 +1740,13 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
         <v>8</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1805,15 +1805,15 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
         <v>1.5</v>
@@ -1823,18 +1823,18 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1859,35 +1859,49 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
       <c r="S19" t="n">
         <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1895,7 +1909,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1915,54 +1929,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2011,16 +2011,16 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -2031,13 +2031,13 @@
         <v>0.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2065,70 +2065,48 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/flower/flower_18.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
         <v>4</v>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2148,48 +2126,70 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2209,27 +2209,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/dog/dog_29.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2243,36 +2239,32 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q24" t="n">
         <v>0.2</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2292,57 +2284,65 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
       <c r="P25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
         <v>0.2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
         <v>6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2451,26 +2451,40 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
       <c r="S27" t="n">
         <v>2</v>
       </c>
@@ -2483,7 +2497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2503,70 +2517,48 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_10.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2586,23 +2578,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2616,27 +2612,31 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
       <c r="P29" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0.2</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
         <v>1.5</v>
@@ -2716,10 +2716,10 @@
         <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2765,16 +2765,16 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         <v>0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="n">
         <v>4</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2819,27 +2819,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2855,34 +2851,30 @@
       <c r="M32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>3</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
         <v>0.2</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2902,40 +2894,54 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -2963,27 +2969,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2997,11 +3003,11 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3015,18 +3021,18 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3046,54 +3052,40 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3101,7 +3093,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3121,23 +3113,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3151,32 +3147,36 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
       <c r="P36" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q36" t="n">
         <v>0.2</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
         <v>8</v>
       </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3196,54 +3196,40 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3271,12 +3257,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3292,16 +3278,16 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -3312,13 +3298,13 @@
         <v>0.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3346,49 +3332,49 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
         <v>1.5</v>
@@ -3398,13 +3384,13 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3429,49 +3415,49 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>outside</t>
+          <t>inside</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
         <v>1.5</v>
@@ -3481,18 +3467,18 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3512,40 +3498,54 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3587,11 +3587,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3655,16 +3655,16 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         <v>0.2</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -3689,7 +3689,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3709,57 +3709,65 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M44" t="n">
         <v>2</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
       <c r="P44" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q44" t="n">
         <v>0.2</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3784,27 +3792,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3818,7 +3826,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3826,7 +3834,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P45" t="n">
         <v>1.5</v>
@@ -3836,18 +3844,18 @@
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3867,27 +3875,23 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_37.jpg</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_29.jpg</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3901,36 +3905,32 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q46" t="n">
         <v>0.2</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
       <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="n">
         <v>6</v>
       </c>
-      <c r="T46" t="n">
-        <v>9</v>
-      </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3950,62 +3950,70 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>5</v>
+      </c>
       <c r="P47" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q47" t="n">
         <v>0.2</v>
       </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4025,40 +4033,54 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_02.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R48" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
       <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="n">
         <v>6</v>
-      </c>
-      <c r="T48" t="n">
-        <v>10</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4066,7 +4088,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4086,23 +4108,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4116,32 +4142,36 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>5</v>
+      </c>
       <c r="P49" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q49" t="n">
         <v>0.2</v>
       </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
         <v>7</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4161,27 +4191,23 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4197,34 +4223,30 @@
       <c r="M50" t="n">
         <v>1</v>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>3</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
       </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4244,70 +4266,48 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_10.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>3</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T51" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4327,70 +4327,48 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4410,62 +4388,70 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
       <c r="P53" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q53" t="n">
         <v>0.2</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4485,70 +4471,62 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O54" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q54" t="n">
         <v>0.2</v>
       </c>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4568,40 +4546,54 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R55" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4609,7 +4601,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4629,23 +4621,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_29.jpg</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4659,32 +4655,36 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
       <c r="P56" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q56" t="n">
         <v>0.2</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4704,62 +4704,70 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
       <c r="P57" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q57" t="n">
         <v>0.2</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="n">
         <v>6</v>
       </c>
-      <c r="T57" t="n">
-        <v>10</v>
-      </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4779,48 +4787,70 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>7</v>
+      </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -4840,27 +4870,23 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
           <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4876,34 +4902,30 @@
       <c r="M59" t="n">
         <v>1</v>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O59" t="n">
-        <v>2</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q59" t="n">
         <v>0.2</v>
       </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U59" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4923,65 +4945,43 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O60" t="n">
-        <v>7</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>8</v>
       </c>
-      <c r="T60" t="n">
-        <v>10</v>
-      </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_39.jpg</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T61" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>

--- a/sequences/retrieval_blockB_fixed-middle-10_01.xlsx
+++ b/sequences/retrieval_blockB_fixed-middle-10_01.xlsx
@@ -557,12 +557,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -587,10 +587,10 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -618,37 +618,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>1.5</v>
@@ -670,13 +670,13 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -701,12 +701,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -781,65 +781,57 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.2</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="S5" t="n">
         <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -859,23 +851,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -889,27 +885,31 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -934,12 +934,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -964,10 +964,10 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -995,27 +995,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1122,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1153,70 +1153,62 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0.2</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
       <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1236,62 +1228,70 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_10.jpg</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
       <c r="P11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0.2</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1311,57 +1311,65 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
       <c r="P12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0.2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1386,12 +1394,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1416,7 +1424,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1430,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1441,7 +1449,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1461,65 +1469,57 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.2</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1605,49 +1605,49 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
         <v>1.5</v>
@@ -1657,13 +1657,13 @@
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
         <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1722,15 +1722,15 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
         <v>1.5</v>
@@ -1740,18 +1740,18 @@
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1771,65 +1771,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1854,12 +1832,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1884,7 +1862,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1898,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1909,7 +1887,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1929,40 +1907,54 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1970,7 +1962,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1990,62 +1982,70 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>stimuli/flower/flower_39.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
       <c r="P21" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.2</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2065,40 +2065,54 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R22" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2106,7 +2120,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2126,27 +2140,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2160,36 +2170,32 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0.2</v>
       </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2209,7 +2215,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2217,54 +2223,62 @@
           <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
       <c r="P24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.2</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
         <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2284,70 +2298,48 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_26.jpg</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_18.jpg</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
         <v>4</v>
       </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2367,62 +2359,70 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>stimuli/dog/dog_29.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
       <c r="P26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2447,18 +2447,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2472,32 +2476,36 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
       <c r="P27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.2</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2517,40 +2525,54 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2558,7 +2580,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2578,70 +2600,48 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2661,27 +2661,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_02.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2695,36 +2691,32 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0.2</v>
       </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2744,57 +2736,65 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>5</v>
+      </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0.2</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/flower/flower_18.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
+          <t>stimuli/ball/ball_30.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
         <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2969,70 +2969,48 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_30.jpg</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3052,43 +3030,65 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -3118,36 +3118,36 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
         <v>1.5</v>
@@ -3168,15 +3168,15 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3196,40 +3196,54 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3237,7 +3251,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3257,23 +3271,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_07.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3287,32 +3305,36 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
       <c r="P38" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q38" t="n">
         <v>0.2</v>
       </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
         <v>6</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3332,27 +3354,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3366,31 +3384,27 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q39" t="n">
         <v>0.2</v>
       </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3415,49 +3429,49 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_29.jpg</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P40" t="n">
         <v>1.5</v>
@@ -3467,18 +3481,18 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3498,54 +3512,40 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3573,43 +3573,65 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3634,12 +3656,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_30.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -3678,10 +3700,10 @@
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3709,37 +3731,37 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_18.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_33.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -3751,7 +3773,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
         <v>1.5</v>
@@ -3761,18 +3783,18 @@
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T44" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3792,65 +3814,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_33.jpg</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_30.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_18.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -3919,10 +3919,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3958,19 +3958,15 @@
           <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_18.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3984,36 +3980,32 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q47" t="n">
         <v>0.2</v>
       </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T47" t="n">
         <v>5</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4033,7 +4025,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/chair/chair_29.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4041,54 +4033,62 @@
           <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_06.jpg</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>5</v>
+      </c>
       <c r="P48" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
         <v>0.2</v>
       </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
         <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4108,70 +4108,48 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>stimuli/house/house_30.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_21.jpg</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_02.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4196,18 +4174,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_30.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_39.jpg</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_39.jpg</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4221,32 +4203,36 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>5</v>
+      </c>
       <c r="P50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
         <v>4</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4266,40 +4252,54 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
+          <t>stimuli/jacket/jacket_02.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
+          <t>stimuli/hammer/hammer_06.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4327,40 +4327,54 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_33.jpg</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/chair/chair_18.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4388,49 +4402,49 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/hammer/hammer_03.jpg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_37.jpg</t>
+          <t>stimuli/bicycle/bicycle_26.jpg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>outside</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
         <v>1.5</v>
@@ -4440,18 +4454,18 @@
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4471,23 +4485,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/dog/dog_29.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_18.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>stimuli/house/house_37.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_37.jpg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4501,32 +4519,36 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
       <c r="P54" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q54" t="n">
         <v>0.2</v>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4546,54 +4568,40 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_19.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_33.jpg</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_03.jpg</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4601,7 +4609,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4621,27 +4629,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_29.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_18.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_29.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4655,36 +4659,32 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q56" t="n">
         <v>0.2</v>
       </c>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4709,22 +4709,18 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_07.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_07.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4738,36 +4734,32 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O57" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Q57" t="n">
         <v>0.2</v>
       </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
       <c r="S57" t="n">
         <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4787,65 +4779,43 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_29.jpg</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_06.jpg</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_21.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O58" t="n">
-        <v>7</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4875,7 +4845,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_02.jpg</t>
+          <t>stimuli/dog/dog_07.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4891,12 +4861,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -4911,13 +4881,13 @@
         <v>0.2</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -4925,7 +4895,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4945,48 +4915,70 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_21.jpg</t>
+          <t>stimuli/bread/bread_10.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_03.jpg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_29.jpg</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_30.jpg</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>6</v>
+      </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T60" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5006,57 +4998,65 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_39.jpg</t>
+          <t>stimuli/ball/ball_21.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_10.jpg</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>stimuli/hand/hand_03.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_03.jpg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bicycle/bicycle_18.jpg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>3</v>
+      </c>
       <c r="P61" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q61" t="n">
         <v>0.2</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
